--- a/Collections/EURO/Portugal/#EURO#Portugal#Commemorative#[2007-present]#UNC.xlsx
+++ b/Collections/EURO/Portugal/#EURO#Portugal#Commemorative#[2007-present]#UNC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Portugal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7BE0C45-B97C-44F6-95C5-464F4D1BED88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB35426-1094-4D79-A7DF-D9A3BF40635A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4170" yWindow="1430" windowWidth="33150" windowHeight="17560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2€" sheetId="1" r:id="rId1"/>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="89">
   <si>
     <t>Year</t>
   </si>
@@ -360,6 +360,12 @@
   </si>
   <si>
     <t>Sustainable Development</t>
+  </si>
+  <si>
+    <t>70th Anniversary - Calouste Gulbenkian Foundation</t>
+  </si>
+  <si>
+    <t>100th Anniversary - Rotary in Portugal</t>
   </si>
 </sst>
 </file>
@@ -647,7 +653,23 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -774,9 +796,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="3" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1045,7 +1067,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="12" customWidth="1"/>
@@ -2052,6 +2074,54 @@
         <v/>
       </c>
     </row>
+    <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="22">
+        <v>2026</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C39" s="8"/>
+      <c r="D39" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="F39" s="8"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="10">
+        <v>0</v>
+      </c>
+      <c r="I39" s="11" t="str">
+        <f t="shared" ref="I39:I40" si="8">IF(OR(AND(H39&gt;1,H39&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="22">
+        <v>2026</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C40" s="8"/>
+      <c r="D40" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="F40" s="8"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="10">
+        <v>0</v>
+      </c>
+      <c r="I40" s="11" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B2:G2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="2">
@@ -2059,11 +2129,28 @@
     <mergeCell ref="C1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="H22:H26 H3:H20">
-    <cfRule type="containsText" dxfId="14" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="16" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H22:H26 H3:H20">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H21">
+    <cfRule type="containsText" dxfId="15" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H21))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H21">
     <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2075,12 +2162,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H21">
+  <conditionalFormatting sqref="H27">
+    <cfRule type="containsText" dxfId="14" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H27">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H28">
     <cfRule type="containsText" dxfId="13" priority="27" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H21))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H21">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H28">
     <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2092,12 +2196,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H27">
+  <conditionalFormatting sqref="H29">
     <cfRule type="containsText" dxfId="12" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H27))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H27">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29">
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2109,12 +2213,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H28">
+  <conditionalFormatting sqref="H30">
     <cfRule type="containsText" dxfId="11" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H28))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H28">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H30))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H30">
     <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2126,29 +2230,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H29">
-    <cfRule type="containsText" dxfId="10" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H29">
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H30">
-    <cfRule type="containsText" dxfId="9" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H30))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H30">
+  <conditionalFormatting sqref="H31 H33">
+    <cfRule type="containsText" dxfId="10" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H31))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H31 H33">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2160,12 +2247,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H31 H33">
+  <conditionalFormatting sqref="H32 H34">
+    <cfRule type="containsText" dxfId="9" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H32))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H34 H32">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H35">
     <cfRule type="containsText" dxfId="8" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H31))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H33 H31">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H35))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H35">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2177,12 +2281,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H32 H34">
+  <conditionalFormatting sqref="H36">
     <cfRule type="containsText" dxfId="7" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H32))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H32 H34">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H36))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H36">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2194,13 +2298,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H35">
-    <cfRule type="containsText" dxfId="6" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H35))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H35">
-    <cfRule type="colorScale" priority="12">
+  <conditionalFormatting sqref="H37">
+    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H37))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H37">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -2211,13 +2315,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H36">
-    <cfRule type="containsText" dxfId="5" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H36))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H36">
-    <cfRule type="colorScale" priority="10">
+  <conditionalFormatting sqref="H38">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H38))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H38">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -2228,12 +2332,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H37">
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H37))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H37">
+  <conditionalFormatting sqref="H39">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H39))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H39">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2245,12 +2349,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H38">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H38))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H38">
+  <conditionalFormatting sqref="H40">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H40))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H40">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
